--- a/src/assets/template/Client.xlsx
+++ b/src/assets/template/Client.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Angular_Workspace\taskappnew\src\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6509B0-C682-45A5-84E9-D6A53F105C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749FA405-1DF2-4009-8142-29C16BA2482A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1193D5F1-C798-48BE-B22D-5C01532F52FC}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Sr No</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>Society Manager Email</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
@@ -597,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5B2CC56-B6F9-4F1A-A714-5A5638ED1F2E}">
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.77734375" customWidth="1"/>
@@ -617,12 +620,12 @@
     <col min="26" max="26" width="11.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -700,6 +703,9 @@
       </c>
       <c r="Z2" t="s">
         <v>22</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/template/Client.xlsx
+++ b/src/assets/template/Client.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Angular_Workspace\taskappnew\src\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749FA405-1DF2-4009-8142-29C16BA2482A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E95097A-385E-4960-9D9F-6013D7B027B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1193D5F1-C798-48BE-B22D-5C01532F52FC}"/>
   </bookViews>
@@ -78,24 +78,6 @@
     <t>Contact Email</t>
   </si>
   <si>
-    <t>Contact Person 1 Name</t>
-  </si>
-  <si>
-    <t>Contact Person 1 Email</t>
-  </si>
-  <si>
-    <t>Contact Person 2 Name</t>
-  </si>
-  <si>
-    <t>Contact Person 2 Email</t>
-  </si>
-  <si>
-    <t>Contact Person 3 Name</t>
-  </si>
-  <si>
-    <t>Contact Person 3 Email</t>
-  </si>
-  <si>
     <t>Start Date</t>
   </si>
   <si>
@@ -226,13 +208,31 @@
     </r>
   </si>
   <si>
-    <t>Other Emails</t>
-  </si>
-  <si>
     <t>Society Manager Email</t>
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Chairman’s Name</t>
+  </si>
+  <si>
+    <t>Chairman’s Email ID</t>
+  </si>
+  <si>
+    <t>Secretary’s Name</t>
+  </si>
+  <si>
+    <t>Secretary’s Email ID</t>
+  </si>
+  <si>
+    <t>Treasurer’s Name</t>
+  </si>
+  <si>
+    <t>Treasurer’s Email ID</t>
+  </si>
+  <si>
+    <t>CC Email</t>
   </si>
 </sst>
 </file>
@@ -622,7 +622,7 @@
   <sheetData>
     <row r="1" spans="1:27" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
@@ -630,7 +630,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -648,7 +648,7 @@
         <v>5</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
         <v>6</v>
@@ -675,37 +675,37 @@
         <v>13</v>
       </c>
       <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X2" t="s">
         <v>14</v>
       </c>
-      <c r="R2" t="s">
+      <c r="Y2" t="s">
         <v>15</v>
       </c>
-      <c r="S2" t="s">
+      <c r="Z2" t="s">
         <v>16</v>
       </c>
-      <c r="T2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U2" t="s">
-        <v>18</v>
-      </c>
-      <c r="V2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="AA2" t="s">
         <v>20</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/template/Client.xlsx
+++ b/src/assets/template/Client.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Angular_Workspace\taskappnew\src\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E95097A-385E-4960-9D9F-6013D7B027B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FEAA54-D4D1-4B9A-A7E2-D323CFCA3EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1193D5F1-C798-48BE-B22D-5C01532F52FC}"/>
   </bookViews>
@@ -87,9 +87,6 @@
     <t>Outstanding</t>
   </si>
   <si>
-    <t>Tax Payable</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -233,6 +230,9 @@
   </si>
   <si>
     <t>CC Email</t>
+  </si>
+  <si>
+    <t>Tax Applicable</t>
   </si>
 </sst>
 </file>
@@ -622,7 +622,7 @@
   <sheetData>
     <row r="1" spans="1:27" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
@@ -630,7 +630,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -648,7 +648,7 @@
         <v>5</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
         <v>6</v>
@@ -675,25 +675,25 @@
         <v>13</v>
       </c>
       <c r="Q2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" t="s">
         <v>21</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>22</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>23</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>24</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>25</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>26</v>
-      </c>
-      <c r="W2" t="s">
-        <v>27</v>
       </c>
       <c r="X2" t="s">
         <v>14</v>
@@ -705,7 +705,7 @@
         <v>16</v>
       </c>
       <c r="AA2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/template/Client.xlsx
+++ b/src/assets/template/Client.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Angular_Workspace\taskappnew\src\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FEAA54-D4D1-4B9A-A7E2-D323CFCA3EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0C5FF2-FBBF-4B46-8EE1-C4075639829A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1193D5F1-C798-48BE-B22D-5C01532F52FC}"/>
   </bookViews>
@@ -87,6 +87,36 @@
     <t>Outstanding</t>
   </si>
   <si>
+    <t>Society Manager Email</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Chairman’s Name</t>
+  </si>
+  <si>
+    <t>Chairman’s Email ID</t>
+  </si>
+  <si>
+    <t>Secretary’s Name</t>
+  </si>
+  <si>
+    <t>Secretary’s Email ID</t>
+  </si>
+  <si>
+    <t>Treasurer’s Name</t>
+  </si>
+  <si>
+    <t>Treasurer’s Email ID</t>
+  </si>
+  <si>
+    <t>CC Email</t>
+  </si>
+  <si>
+    <t>Tax Applicable</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -138,7 +168,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Tax Payable</t>
+      <t>Tax Applicable</t>
     </r>
     <r>
       <rPr>
@@ -203,36 +233,6 @@
       </rPr>
       <t xml:space="preserve"> (,)</t>
     </r>
-  </si>
-  <si>
-    <t>Society Manager Email</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Chairman’s Name</t>
-  </si>
-  <si>
-    <t>Chairman’s Email ID</t>
-  </si>
-  <si>
-    <t>Secretary’s Name</t>
-  </si>
-  <si>
-    <t>Secretary’s Email ID</t>
-  </si>
-  <si>
-    <t>Treasurer’s Name</t>
-  </si>
-  <si>
-    <t>Treasurer’s Email ID</t>
-  </si>
-  <si>
-    <t>CC Email</t>
-  </si>
-  <si>
-    <t>Tax Applicable</t>
   </si>
 </sst>
 </file>
@@ -622,7 +622,7 @@
   <sheetData>
     <row r="1" spans="1:27" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
@@ -630,7 +630,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -648,7 +648,7 @@
         <v>5</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
         <v>6</v>
@@ -675,25 +675,25 @@
         <v>13</v>
       </c>
       <c r="Q2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" t="s">
         <v>20</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>21</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>22</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>23</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>24</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>25</v>
-      </c>
-      <c r="W2" t="s">
-        <v>26</v>
       </c>
       <c r="X2" t="s">
         <v>14</v>
@@ -705,7 +705,7 @@
         <v>16</v>
       </c>
       <c r="AA2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/template/Client.xlsx
+++ b/src/assets/template/Client.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Angular_Workspace\taskappnew\src\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0C5FF2-FBBF-4B46-8EE1-C4075639829A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5D2F05-0C6D-4AFD-A3B1-84608B3BD1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1193D5F1-C798-48BE-B22D-5C01532F52FC}"/>
   </bookViews>
@@ -114,7 +114,7 @@
     <t>CC Email</t>
   </si>
   <si>
-    <t>Tax Applicable</t>
+    <t>TDS Applicable</t>
   </si>
   <si>
     <r>
@@ -168,7 +168,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Tax Applicable</t>
+      <t>TDS Applicable</t>
     </r>
     <r>
       <rPr>
